--- a/TestCase/Nhom_9_System_Test.xlsx
+++ b/TestCase/Nhom_9_System_Test.xlsx
@@ -598,15 +598,15 @@
   <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
